--- a/artfynd/A 41204-2023 artfynd.xlsx
+++ b/artfynd/A 41204-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 41204-2023 artfynd.xlsx
+++ b/artfynd/A 41204-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,59 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>101959961</v>
+        <v>101959959</v>
       </c>
       <c r="B2" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>N Ulvsbomuren, Vstm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>559726.8547407261</v>
+        <v>559752</v>
       </c>
       <c r="R2" t="n">
-        <v>6631047.59559757</v>
+        <v>6631071</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -757,21 +743,11 @@
           <t>2022-04-21</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-04-21</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -784,6 +760,21 @@
       <c r="AI2" t="inlineStr">
         <is>
           <t>Äldre barrskog</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Granlåga # Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -801,50 +792,54 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>101959959</v>
+        <v>101959950</v>
       </c>
       <c r="B3" t="n">
-        <v>94121</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>N Ulvsbomuren, Vstm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>559752.1788889276</v>
+        <v>559609</v>
       </c>
       <c r="R3" t="n">
-        <v>6631071.145844752</v>
+        <v>6631091</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -874,21 +869,11 @@
           <t>2022-04-21</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-04-21</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -901,21 +886,6 @@
       <c r="AI3" t="inlineStr">
         <is>
           <t>Äldre barrskog</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Granlåga # Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -936,12 +906,7 @@
         <v>101959960</v>
       </c>
       <c r="B4" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -982,10 +947,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>559726.5961460314</v>
+        <v>559726</v>
       </c>
       <c r="R4" t="n">
-        <v>6631063.691141052</v>
+        <v>6631063</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1015,19 +980,9 @@
           <t>2022-04-21</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2022-04-21</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1056,6 +1011,242 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>101959961</v>
+      </c>
+      <c r="B5" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>N Ulvsbomuren, Vstm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>559727</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6631048</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2022-04-21</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2022-04-21</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Äldre barrskog</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Jacob Rudhe</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Jacob Rudhe</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>104501633</v>
+      </c>
+      <c r="B6" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Ulvsbomuren, N om (knärot), Vstm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>559727</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6631064</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>U-Sur-0494</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2022-04-21</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2022-04-21</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>X: (10), 10 pl, A: 572/619 (10),2 pl</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>äldre barrskog</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Bo Eriksson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Jacob Rudhe</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 41204-2023 artfynd.xlsx
+++ b/artfynd/A 41204-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -789,6 +794,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101959959</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -900,6 +910,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101959950</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1011,6 +1026,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101959960</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1122,6 +1142,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101959961</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1247,8 +1272,20 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104501633</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>